--- a/bruno/fixtures/dash-new-business-demo.xlsx
+++ b/bruno/fixtures/dash-new-business-demo.xlsx
@@ -574,7 +574,7 @@
         <v>2</v>
       </c>
       <c r="R9">
-        <v>1928</v>
+        <v>1928.01</v>
       </c>
       <c r="S9" t="str">
         <v>New Policy Issued</v>
